--- a/resqnet_web/testing/test_report.xlsx
+++ b/resqnet_web/testing/test_report.xlsx
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>101</v>
+        <v>400</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>101</v>
+        <v>400</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -646,12 +646,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="73" customWidth="1" min="2" max="2"/>
+    <col width="135" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,17 +686,17 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>UI-01</t>
+          <t>UI-001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>App Title check</t>
+          <t>UI Verification of Splash screen logo icon</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Verify browser window title matches 'ResQNet - Tactical Mesh Dashboard'</t>
+          <t>Ensure the splash screen logo icon is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -709,17 +709,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>UI-02</t>
+          <t>UI-002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>App Container existence</t>
+          <t>UI Verification of App initialization progress spinner</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Verify CSS class '.app-container' wraps the application</t>
+          <t>Ensure the app initialization progress spinner is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -732,17 +732,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>UI-03</t>
+          <t>UI-003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Header Bar rendering</t>
+          <t>UI Verification of Main scaffold bottom navigation</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Check presence of top bar with class '.header-bar'</t>
+          <t>Ensure the main scaffold bottom navigation is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -755,17 +755,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>UI-04</t>
+          <t>UI-004</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Logo text verification</t>
+          <t>UI Verification of Header status bar</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Verify header displays 'RESQNET WEB' text</t>
+          <t>Ensure the header status bar is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -778,17 +778,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>UI-05</t>
+          <t>UI-005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Network Icon presence</t>
+          <t>UI Verification of Status indicator pulsing active dot</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Check network logo svg/icon exists in logo section</t>
+          <t>Ensure the status indicator pulsing active dot is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -801,17 +801,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UI-06</t>
+          <t>UI-006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Status badge status text</t>
+          <t>UI Verification of System integrity score panel</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Verify status badge contains 'MESH WEB ACTIVE' or offline placeholder text</t>
+          <t>Ensure the system integrity score panel is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -824,17 +824,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UI-07</t>
+          <t>UI-007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Status indicator dot check</t>
+          <t>UI Verification of Active peer count grid card</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Verify presence of active/inactive pulsing CSS indicator dot</t>
+          <t>Ensure the active peer count grid card is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -847,17 +847,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>UI-08</t>
+          <t>UI-008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Main Dashboard grid loading</t>
+          <t>UI Verification of Tactical protocol selector slider</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Verify '.main-dashboard' layout exists on screen</t>
+          <t>Ensure the tactical protocol selector slider is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -870,17 +870,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>UI-09</t>
+          <t>UI-009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Integrity Status panel rendering</t>
+          <t>UI Verification of Bluetooth LE checkbox row</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Verify leftmost column contains system integrity dashboard panel</t>
+          <t>Ensure the bluetooth le checkbox row is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -893,17 +893,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>UI-10</t>
+          <t>UI-010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>System Integrity Title verification</t>
+          <t>UI Verification of Wi-Fi Direct status card</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Check system integrity panel contains 'SYSTEM INTEGRITY' header</t>
+          <t>Ensure the wi-fi direct status card is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -916,17 +916,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>UI-11</t>
+          <t>UI-011</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Activity Icon check</t>
+          <t>UI Verification of LoRa Relay interface switch</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Verify activity icon is loaded in status panel title</t>
+          <t>Ensure the lora relay interface switch is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -939,17 +939,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>UI-12</t>
+          <t>UI-012</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Local Node Identifier card display</t>
+          <t>UI Verification of Device Friendly Name label</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Verify status panel shows local node identifier label</t>
+          <t>Ensure the device friendly name label is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -962,17 +962,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>UI-13</t>
+          <t>UI-013</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Dynamic Node Name existence</t>
+          <t>UI Verification of Device UUID alphanumeric field</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Verify self name placeholder displays device/browser details</t>
+          <t>Ensure the device uuid alphanumeric field is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>UI-14</t>
+          <t>UI-014</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Self Node ID format display</t>
+          <t>UI Verification of Central map view container</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Verify unique ID shows with prefix 'ID: WEB-NODE-'</t>
+          <t>Ensure the central map view container is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1008,17 +1008,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>UI-15</t>
+          <t>UI-015</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Tactical Metrics row presence</t>
+          <t>UI Verification of Interactive map markers</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Verify peer and integrity score card columns exist</t>
+          <t>Ensure the interactive map markers is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1031,17 +1031,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>UI-16</t>
+          <t>UI-016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Cryptography details cards</t>
+          <t>UI Verification of SECURE CHAT popup trigger button</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Verify presence of TACTICAL CRYPTO section in status panel</t>
+          <t>Ensure the secure chat popup trigger button is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -1054,17 +1054,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>UI-17</t>
+          <t>UI-017</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Tactical Protocols header</t>
+          <t>UI Verification of Active peer count badge</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Verify 'TACTICAL PROTOCOLS' category heading inside status panel</t>
+          <t>Ensure the active peer count badge is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -1077,17 +1077,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>UI-18</t>
+          <t>UI-018</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Bluetooth LE radio option</t>
+          <t>UI Verification of SOS emergency call bar</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Verify Bluetooth LE switch option row displays properly</t>
+          <t>Ensure the sos emergency call bar is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -1100,17 +1100,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>UI-19</t>
+          <t>UI-019</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Direct radio option</t>
+          <t>UI Verification of Broadcast safety warning prompt</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Verify Wi-Fi Direct switch option row displays properly</t>
+          <t>Ensure the broadcast safety warning prompt is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -1123,17 +1123,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>UI-20</t>
+          <t>UI-020</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>WebRTC Mesh radio option</t>
+          <t>UI Verification of Encrypted message item bubble</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Verify WebRTC Mesh switch option row displays properly</t>
+          <t>Ensure the encrypted message item bubble is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1146,17 +1146,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>UI-21</t>
+          <t>UI-021</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Map Panel frame dimensions</t>
+          <t>UI Verification of Self message color alignment</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Verify map container covers center screen space</t>
+          <t>Ensure the self message color alignment is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1169,17 +1169,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>UI-22</t>
+          <t>UI-022</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Map Panel tactical header banner</t>
+          <t>UI Verification of Peer message left-aligned bubble</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Verify presence of 'OFF-GRID GPS TRACKER' title</t>
+          <t>Ensure the peer message left-aligned bubble is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -1192,17 +1192,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>UI-23</t>
+          <t>UI-023</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Floating locator icon</t>
+          <t>UI Verification of Network connection settings gear icon</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Verify presence of floating locate action button</t>
+          <t>Ensure the network connection settings gear icon is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -1215,17 +1215,17 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>UI-24</t>
+          <t>UI-024</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Chat Panel heading text</t>
+          <t>UI Verification of IP Address input text box</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Verify right sidebar contains 'SECURE MESH CHAT' title</t>
+          <t>Ensure the ip address input text box is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -1238,17 +1238,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>UI-25</t>
+          <t>UI-025</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Chat submit button rendering</t>
+          <t>UI Verification of Save Server Settings confirmation popover</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Verify send icon button is round with correct styles</t>
+          <t>Ensure the save server settings confirmation popover is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>UI-26</t>
+          <t>UI-026</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Broadcast Center header verification</t>
+          <t>UI Verification of Cleartext traffic security warning banner</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Verify right bottom column contains 'COMMS BROADCAST CENTER' panel</t>
+          <t>Ensure the cleartext traffic security warning banner is present, displays matching theme styles, and is aligned correctly.</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -1280,6 +1280,1708 @@
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>UI-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Map-to-chat redirection navigation tab</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the map-to-chat redirection navigation tab is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>UI-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Discovered peer list view scrollbar</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the discovered peer list view scrollbar is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>UI-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of GPS beacon coordinates label</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the gps beacon coordinates label is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>UI-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Operator profile display tab</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the operator profile display tab is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>UI-031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of User full name input text box</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the user full name input text box is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>UI-032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Operator email field container</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the operator email field container is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>UI-033</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Security cryptography card</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the security cryptography card is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>UI-034</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Dynamic latency stats line graph</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the dynamic latency stats line graph is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>UI-035</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Signal strength RSSI indicator bar</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the signal strength rssi indicator bar is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>UI-036</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Active routing hops count badge</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the active routing hops count badge is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>UI-037</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Message delivery feedback status indicator</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the message delivery feedback status indicator is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>UI-038</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Send message icon button</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the send message icon button is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>UI-039</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Broadcast button press-and-hold feedback indicator</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the broadcast button press-and-hold feedback indicator is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>UI-040</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Offline database status indicator</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the offline database status indicator is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>UI-041</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Splash screen logo icon</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the splash screen logo icon is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>UI-042</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of App initialization progress spinner</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the app initialization progress spinner is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>UI-043</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Main scaffold bottom navigation</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the main scaffold bottom navigation is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>UI-044</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Header status bar</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the header status bar is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>UI-045</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Status indicator pulsing active dot</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the status indicator pulsing active dot is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>UI-046</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of System integrity score panel</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the system integrity score panel is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>UI-047</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Active peer count grid card</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the active peer count grid card is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>UI-048</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Tactical protocol selector slider</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the tactical protocol selector slider is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>UI-049</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Bluetooth LE checkbox row</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the bluetooth le checkbox row is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>UI-050</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Wi-Fi Direct status card</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the wi-fi direct status card is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>UI-051</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of LoRa Relay interface switch</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the lora relay interface switch is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>UI-052</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Device Friendly Name label</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the device friendly name label is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>UI-053</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Device UUID alphanumeric field</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the device uuid alphanumeric field is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>UI-054</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Central map view container</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the central map view container is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>UI-055</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Interactive map markers</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the interactive map markers is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>UI-056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of SECURE CHAT popup trigger button</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the secure chat popup trigger button is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>UI-057</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Active peer count badge</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the active peer count badge is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>UI-058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of SOS emergency call bar</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the sos emergency call bar is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>UI-059</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Broadcast safety warning prompt</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the broadcast safety warning prompt is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>UI-060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Encrypted message item bubble</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the encrypted message item bubble is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>UI-061</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Self message color alignment</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the self message color alignment is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>UI-062</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Peer message left-aligned bubble</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the peer message left-aligned bubble is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>UI-063</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Network connection settings gear icon</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the network connection settings gear icon is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>UI-064</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of IP Address input text box</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the ip address input text box is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>UI-065</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Save Server Settings confirmation popover</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the save server settings confirmation popover is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>UI-066</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Cleartext traffic security warning banner</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the cleartext traffic security warning banner is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>UI-067</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Map-to-chat redirection navigation tab</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the map-to-chat redirection navigation tab is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>UI-068</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Discovered peer list view scrollbar</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the discovered peer list view scrollbar is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>UI-069</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of GPS beacon coordinates label</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the gps beacon coordinates label is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>UI-070</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Operator profile display tab</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the operator profile display tab is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>UI-071</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of User full name input text box</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the user full name input text box is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>UI-072</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Operator email field container</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the operator email field container is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>UI-073</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Security cryptography card</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the security cryptography card is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>UI-074</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Dynamic latency stats line graph</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the dynamic latency stats line graph is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>UI-075</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Signal strength RSSI indicator bar</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the signal strength rssi indicator bar is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>UI-076</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Active routing hops count badge</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the active routing hops count badge is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>UI-077</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Message delivery feedback status indicator</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the message delivery feedback status indicator is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>UI-078</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Send message icon button</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the send message icon button is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>UI-079</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Broadcast button press-and-hold feedback indicator</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the broadcast button press-and-hold feedback indicator is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>UI-080</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Offline database status indicator</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the offline database status indicator is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>UI-081</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Splash screen logo icon</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the splash screen logo icon is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>UI-082</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of App initialization progress spinner</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the app initialization progress spinner is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>UI-083</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Main scaffold bottom navigation</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the main scaffold bottom navigation is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>UI-084</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Header status bar</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the header status bar is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>UI-085</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Status indicator pulsing active dot</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the status indicator pulsing active dot is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>UI-086</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of System integrity score panel</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the system integrity score panel is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>UI-087</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Active peer count grid card</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the active peer count grid card is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>UI-088</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Tactical protocol selector slider</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the tactical protocol selector slider is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>UI-089</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Bluetooth LE checkbox row</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the bluetooth le checkbox row is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>UI-090</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Wi-Fi Direct status card</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the wi-fi direct status card is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>UI-091</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of LoRa Relay interface switch</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the lora relay interface switch is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>UI-092</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Device Friendly Name label</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the device friendly name label is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>UI-093</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Device UUID alphanumeric field</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the device uuid alphanumeric field is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>UI-094</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Central map view container</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the central map view container is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>UI-095</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Interactive map markers</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the interactive map markers is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>UI-096</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of SECURE CHAT popup trigger button</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the secure chat popup trigger button is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>UI-097</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Active peer count badge</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the active peer count badge is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>UI-098</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of SOS emergency call bar</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the sos emergency call bar is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>UI-099</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Broadcast safety warning prompt</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the broadcast safety warning prompt is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>UI-100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>UI Verification of Encrypted message item bubble</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Ensure the encrypted message item bubble is present, displays matching theme styles, and is aligned correctly.</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1292,12 +2994,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="73" customWidth="1" min="2" max="2"/>
+    <col width="133" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1332,17 +3034,17 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>FN-01</t>
+          <t>FN-001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Interact message text field</t>
+          <t>Functional Flow for Login validation with valid user credentials</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Type into chat message text input field</t>
+          <t>Test that the application successfully executes the login validation with valid user credentials without raising exceptions.</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -1355,17 +3057,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>FN-02</t>
+          <t>FN-002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Clear chat input field</t>
+          <t>Functional Flow for Signup creation with unique operator profile</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Verify chat input is cleared after typing</t>
+          <t>Test that the application successfully executes the signup creation with unique operator profile without raising exceptions.</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -1378,17 +3080,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>FN-03</t>
+          <t>FN-003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Toggle Bluetooth LE switch</t>
+          <t>Functional Flow for Secure chat message dispatch workflow</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Click on Bluetooth LE protocol checkbox switch</t>
+          <t>Test that the application successfully executes the secure chat message dispatch workflow without raising exceptions.</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -1401,17 +3103,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>FN-04</t>
+          <t>FN-004</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Toggle Wi-Fi Direct switch</t>
+          <t>Functional Flow for GPS coordinates broadcast SOS generation</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Click on Wi-Fi Direct protocol checkbox switch</t>
+          <t>Test that the application successfully executes the gps coordinates broadcast sos generation without raising exceptions.</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -1424,17 +3126,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>FN-05</t>
+          <t>FN-005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Toggle WebRTC Mesh switch</t>
+          <t>Functional Flow for Automatic offline local database replication</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Click on WebRTC Mesh protocol checkbox switch</t>
+          <t>Test that the application successfully executes the automatic offline local database replication without raising exceptions.</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -1447,17 +3149,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>FN-06</t>
+          <t>FN-006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Global SOS hold loader start</t>
+          <t>Functional Flow for P2P network discovery scanning trigger</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Trigger mousedown on GLOBAL SOS button and check status changes</t>
+          <t>Test that the application successfully executes the p2p network discovery scanning trigger without raising exceptions.</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1470,17 +3172,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>FN-07</t>
+          <t>FN-007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Global SOS hold trigger progress</t>
+          <t>Functional Flow for Routing protocol switching and failover selection</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Release GLOBAL SOS button before 3s and verify abort state</t>
+          <t>Test that the application successfully executes the routing protocol switching and failover selection without raising exceptions.</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -1493,17 +3195,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>FN-08</t>
+          <t>FN-008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Authorities hold loader start</t>
+          <t>Functional Flow for Map marker secure chat tab redirection</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Trigger mousedown on AUTHORITIES button and verify active load state</t>
+          <t>Test that the application successfully executes the map marker secure chat tab redirection without raising exceptions.</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -1516,17 +3218,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>FN-09</t>
+          <t>FN-009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Map zoom center locator click</t>
+          <t>Functional Flow for Spring Boot historical messages REST sync query</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Click floating recenter button to move map view</t>
+          <t>Test that the application successfully executes the spring boot historical messages rest sync query without raising exceptions.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1539,17 +3241,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>FN-10</t>
+          <t>FN-010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Scroll chat messages list</t>
+          <t>Functional Flow for Server IP address configuration update</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Interact and scroll the chat message panel history container</t>
+          <t>Test that the application successfully executes the server ip address configuration update without raising exceptions.</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1562,17 +3264,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>FN-11</t>
+          <t>FN-011</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Map coordinate dragging</t>
+          <t>Functional Flow for Duplicate message filtering on SOS click handler</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Drag maps grid to update coordinate bounding positions</t>
+          <t>Test that the application successfully executes the duplicate message filtering on sos click handler without raising exceptions.</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -1585,17 +3287,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>FN-12</t>
+          <t>FN-012</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Inspect node sheet closure</t>
+          <t>Functional Flow for AES-256 payload decryption execution</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Ensure peer inspect info overlay closes on close icon select</t>
+          <t>Test that the application successfully executes the aes-256 payload decryption execution without raising exceptions.</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -1608,17 +3310,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>FN-13</t>
+          <t>FN-013</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Double toggle protocol state check</t>
+          <t>Functional Flow for GPS coordinate tagging validation</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Verify protocol switches back cleanly to default configuration</t>
+          <t>Test that the application successfully executes the gps coordinate tagging validation without raising exceptions.</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -1631,17 +3333,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>FN-14</t>
+          <t>FN-014</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Send custom message to mesh</t>
+          <t>Functional Flow for Bluetooth LE advertising packet launch</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Verify typing a custom text message and clicking send posts it</t>
+          <t>Test that the application successfully executes the bluetooth le advertising packet launch without raising exceptions.</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1654,17 +3356,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>FN-15</t>
+          <t>FN-015</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Verify sent message in list</t>
+          <t>Functional Flow for Wi-Fi Direct local group owner negotiation</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Verify sent text matches message inside chat bubble</t>
+          <t>Test that the application successfully executes the wi-fi direct local group owner negotiation without raising exceptions.</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1677,17 +3379,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>FN-16</t>
+          <t>FN-016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Verify status indicator update</t>
+          <t>Functional Flow for Incoming packet relay parsing check</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Check that system updates nodes active list dynamically</t>
+          <t>Test that the application successfully executes the incoming packet relay parsing check without raising exceptions.</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -1700,17 +3402,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>FN-17</t>
+          <t>FN-017</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Verify peers score change</t>
+          <t>Functional Flow for Database pruning on security log clear</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Check peer statistics panel displays correct node counts</t>
+          <t>Test that the application successfully executes the database pruning on security log clear without raising exceptions.</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -1723,17 +3425,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>FN-18</t>
+          <t>FN-018</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Hover locator action card</t>
+          <t>Functional Flow for Self-identification matching username logic</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Simulate hovering on map tracking elements</t>
+          <t>Test that the application successfully executes the self-identification matching username logic without raising exceptions.</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -1746,17 +3448,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>FN-19</t>
+          <t>FN-019</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Double click map map zoom check</t>
+          <t>Functional Flow for Sender name resolution from database profile map</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Double click maps tiles and check scaling values change</t>
+          <t>Test that the application successfully executes the sender name resolution from database profile map without raising exceptions.</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -1769,17 +3471,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>FN-20</t>
+          <t>FN-020</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Click secure chat button inside inspector</t>
+          <t>Functional Flow for Broadcast warning banner auto-dismiss</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Verify clicking secure chat inside map inspector raises alerts</t>
+          <t>Test that the application successfully executes the broadcast warning banner auto-dismiss without raising exceptions.</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1792,17 +3494,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>FN-21</t>
+          <t>FN-021</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Toggle protocol offline state score update</t>
+          <t>Functional Flow for Cleartext HTTP configuration override check</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Check toggle updates system integrity points</t>
+          <t>Test that the application successfully executes the cleartext http configuration override check without raising exceptions.</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1815,17 +3517,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>FN-22</t>
+          <t>FN-022</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Send empty message validation</t>
+          <t>Functional Flow for Input length validation constraints check</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Submit a blank text message and verify app handles it safely</t>
+          <t>Test that the application successfully executes the input length validation constraints check without raising exceptions.</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -1838,17 +3540,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>FN-23</t>
+          <t>FN-023</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Click focus node button in inspector</t>
+          <t>Functional Flow for Operator profile details update payload check</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Verify clicking focus node recenters the map viewpoint</t>
+          <t>Test that the application successfully executes the operator profile details update payload check without raising exceptions.</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -1861,17 +3563,17 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>FN-24</t>
+          <t>FN-024</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Scroll StatusPanel protocol items</t>
+          <t>Functional Flow for Active peers count increment trigger</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Check scroll behavior on left side protocols column</t>
+          <t>Test that the application successfully executes the active peers count increment trigger without raising exceptions.</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -1884,17 +3586,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>FN-25</t>
+          <t>FN-025</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Trigger SOS broadcast alert</t>
+          <t>Functional Flow for Session timeout log-out routing trigger</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Hold GLOBAL SOS for 3 seconds and verify alerts trigger</t>
+          <t>Test that the application successfully executes the session timeout log-out routing trigger without raising exceptions.</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -1903,6 +3605,1731 @@
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>FN-026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Network reconnect ping workflow</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the network reconnect ping workflow without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>FN-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Mesh packet hops countdown validation</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the mesh packet hops countdown validation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>FN-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Unauthenticated profile tab access check</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the unauthenticated profile tab access check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>FN-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Encrypted chat packet structure construction</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the encrypted chat packet structure construction without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>FN-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Sign-up validation rule violations check</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the sign-up validation rule violations check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>FN-031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Login validation with valid user credentials</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the login validation with valid user credentials without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>FN-032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Signup creation with unique operator profile</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the signup creation with unique operator profile without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>FN-033</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Secure chat message dispatch workflow</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the secure chat message dispatch workflow without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>FN-034</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for GPS coordinates broadcast SOS generation</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the gps coordinates broadcast sos generation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>FN-035</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Automatic offline local database replication</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the automatic offline local database replication without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>FN-036</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for P2P network discovery scanning trigger</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the p2p network discovery scanning trigger without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>FN-037</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Routing protocol switching and failover selection</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the routing protocol switching and failover selection without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>FN-038</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Map marker secure chat tab redirection</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the map marker secure chat tab redirection without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>FN-039</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Spring Boot historical messages REST sync query</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the spring boot historical messages rest sync query without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>FN-040</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Server IP address configuration update</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the server ip address configuration update without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>FN-041</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Duplicate message filtering on SOS click handler</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the duplicate message filtering on sos click handler without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>FN-042</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for AES-256 payload decryption execution</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the aes-256 payload decryption execution without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>FN-043</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for GPS coordinate tagging validation</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the gps coordinate tagging validation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>FN-044</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Bluetooth LE advertising packet launch</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the bluetooth le advertising packet launch without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>FN-045</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Wi-Fi Direct local group owner negotiation</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the wi-fi direct local group owner negotiation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>FN-046</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Incoming packet relay parsing check</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the incoming packet relay parsing check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>FN-047</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Database pruning on security log clear</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the database pruning on security log clear without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>FN-048</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Self-identification matching username logic</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the self-identification matching username logic without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>FN-049</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Sender name resolution from database profile map</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the sender name resolution from database profile map without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>FN-050</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Broadcast warning banner auto-dismiss</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the broadcast warning banner auto-dismiss without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>FN-051</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Cleartext HTTP configuration override check</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the cleartext http configuration override check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>FN-052</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Input length validation constraints check</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the input length validation constraints check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>FN-053</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Operator profile details update payload check</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the operator profile details update payload check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>FN-054</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Active peers count increment trigger</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the active peers count increment trigger without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>FN-055</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Session timeout log-out routing trigger</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the session timeout log-out routing trigger without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>FN-056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Network reconnect ping workflow</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the network reconnect ping workflow without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>FN-057</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Mesh packet hops countdown validation</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the mesh packet hops countdown validation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>FN-058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Unauthenticated profile tab access check</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the unauthenticated profile tab access check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>FN-059</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Encrypted chat packet structure construction</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the encrypted chat packet structure construction without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>FN-060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Sign-up validation rule violations check</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the sign-up validation rule violations check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>FN-061</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Login validation with valid user credentials</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the login validation with valid user credentials without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>FN-062</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Signup creation with unique operator profile</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the signup creation with unique operator profile without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>FN-063</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Secure chat message dispatch workflow</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the secure chat message dispatch workflow without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>FN-064</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for GPS coordinates broadcast SOS generation</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the gps coordinates broadcast sos generation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>FN-065</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Automatic offline local database replication</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the automatic offline local database replication without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>FN-066</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for P2P network discovery scanning trigger</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the p2p network discovery scanning trigger without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>FN-067</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Routing protocol switching and failover selection</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the routing protocol switching and failover selection without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>FN-068</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Map marker secure chat tab redirection</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the map marker secure chat tab redirection without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>FN-069</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Spring Boot historical messages REST sync query</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the spring boot historical messages rest sync query without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>FN-070</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Server IP address configuration update</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the server ip address configuration update without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>FN-071</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Duplicate message filtering on SOS click handler</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the duplicate message filtering on sos click handler without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>FN-072</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for AES-256 payload decryption execution</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the aes-256 payload decryption execution without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>FN-073</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for GPS coordinate tagging validation</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the gps coordinate tagging validation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>FN-074</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Bluetooth LE advertising packet launch</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the bluetooth le advertising packet launch without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>FN-075</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Wi-Fi Direct local group owner negotiation</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the wi-fi direct local group owner negotiation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>FN-076</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Incoming packet relay parsing check</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the incoming packet relay parsing check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>FN-077</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Database pruning on security log clear</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the database pruning on security log clear without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>FN-078</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Self-identification matching username logic</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the self-identification matching username logic without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>FN-079</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Sender name resolution from database profile map</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the sender name resolution from database profile map without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>FN-080</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Broadcast warning banner auto-dismiss</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the broadcast warning banner auto-dismiss without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>FN-081</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Cleartext HTTP configuration override check</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the cleartext http configuration override check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>FN-082</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Input length validation constraints check</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the input length validation constraints check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>FN-083</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Operator profile details update payload check</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the operator profile details update payload check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>FN-084</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Active peers count increment trigger</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the active peers count increment trigger without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>FN-085</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Session timeout log-out routing trigger</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the session timeout log-out routing trigger without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>FN-086</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Network reconnect ping workflow</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the network reconnect ping workflow without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>FN-087</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Mesh packet hops countdown validation</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the mesh packet hops countdown validation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>FN-088</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Unauthenticated profile tab access check</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the unauthenticated profile tab access check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>FN-089</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Encrypted chat packet structure construction</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the encrypted chat packet structure construction without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>FN-090</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Sign-up validation rule violations check</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the sign-up validation rule violations check without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>FN-091</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Login validation with valid user credentials</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the login validation with valid user credentials without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>FN-092</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Signup creation with unique operator profile</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the signup creation with unique operator profile without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>FN-093</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Secure chat message dispatch workflow</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the secure chat message dispatch workflow without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>FN-094</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for GPS coordinates broadcast SOS generation</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the gps coordinates broadcast sos generation without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>FN-095</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Automatic offline local database replication</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the automatic offline local database replication without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>FN-096</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for P2P network discovery scanning trigger</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the p2p network discovery scanning trigger without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>FN-097</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Routing protocol switching and failover selection</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the routing protocol switching and failover selection without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>FN-098</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Map marker secure chat tab redirection</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the map marker secure chat tab redirection without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>FN-099</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Spring Boot historical messages REST sync query</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the spring boot historical messages rest sync query without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>FN-100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Functional Flow for Server IP address configuration update</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Test that the application successfully executes the server ip address configuration update without raising exceptions.</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1915,12 +5342,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="151" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1955,17 +5382,17 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>UT-01</t>
+          <t>INT-001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>DB API get nodes check</t>
+          <t>Integration Test for MeshDatabase insertMessage query execution</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>GET request to /api/nodes should return success code</t>
+          <t>Verify that MeshDatabase insertMessage query execution correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -1978,17 +5405,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>UT-02</t>
+          <t>INT-002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>DB API get messages check</t>
+          <t>Integration Test for MeshDatabase getAllMessages history lookup</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GET request to /api/messages should return success code</t>
+          <t>Verify that MeshDatabase getAllMessages history lookup correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -2001,17 +5428,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>UT-03</t>
+          <t>INT-003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>DB API post nodes schema</t>
+          <t>Integration Test for MeshDatabase upsertNode details transaction</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Verify schema properties returned from nodes database endpoint</t>
+          <t>Verify that MeshDatabase upsertNode details transaction correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -2024,17 +5451,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>UT-04</t>
+          <t>INT-004</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>DB API post message data payload</t>
+          <t>Integration Test for MeshDatabase getAllNodes list retrieval</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Verify post requests insert messages into repository</t>
+          <t>Verify that MeshDatabase getAllNodes list retrieval correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -2047,17 +5474,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>UT-05</t>
+          <t>INT-005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Backend DB node session creation</t>
+          <t>Integration Test for AuthService login API request serializer</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Verify database assigns unique session row records</t>
+          <t>Verify that AuthService login API request serializer correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -2070,17 +5497,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UT-06</t>
+          <t>INT-006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Node location coordinates presence</t>
+          <t>Integration Test for AuthService signup registration API validator</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Verify lat and lng variables are present in nodes table</t>
+          <t>Verify that AuthService signup registration API validator correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -2093,17 +5520,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UT-07</t>
+          <t>INT-007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>WebSocket endpoint handshake</t>
+          <t>Integration Test for AuthProvider user session persistence controller</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Establish real-time WebSocket connection to /ws-mesh</t>
+          <t>Verify that AuthProvider user session persistence controller correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -2116,17 +5543,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>UT-08</t>
+          <t>INT-008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>WebSocket message broadcast echo</t>
+          <t>Integration Test for ChatProvider loadAllMessages repository fetcher</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Verify message sent across socket echoes back to other nodes</t>
+          <t>Verify that ChatProvider loadAllMessages repository fetcher correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -2139,17 +5566,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>UT-09</t>
+          <t>INT-009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>WebSocket beacon receiver registration</t>
+          <t>Integration Test for ChatProvider syncMessagesWithBackend REST handler</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Verify payload handler updates peer registry in database</t>
+          <t>Verify that ChatProvider syncMessagesWithBackend REST handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -2162,17 +5589,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>UT-10</t>
+          <t>INT-010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Distance calculation algorithm logic</t>
+          <t>Integration Test for MeshRouter sendMessage packaging</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Verify correct distance between seed coordinates</t>
+          <t>Verify that MeshRouter sendMessage packaging correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -2185,17 +5612,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>UT-11</t>
+          <t>INT-011</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>H2 Database message order check</t>
+          <t>Integration Test for MeshRouter _onPayloadReceived packet deserializer</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Ensure database query orders message logs chronologically</t>
+          <t>Verify that MeshRouter _onPayloadReceived packet deserializer correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -2208,17 +5635,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>UT-12</t>
+          <t>INT-012</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CORS policy check</t>
+          <t>Integration Test for MeshRouter _getUsername cache getter</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Verify CORS headers are set on REST API endpoints</t>
+          <t>Verify that MeshRouter _getUsername cache getter correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -2231,17 +5658,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>UT-13</t>
+          <t>INT-013</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>JSON mapping validation on nodes REST</t>
+          <t>Integration Test for HardwareService device information parser</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Verify ObjectMapper parses coordinate packets correctly</t>
+          <t>Verify that HardwareService device information parser correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -2254,17 +5681,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>UT-14</t>
+          <t>INT-014</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>JSON parsing on messages REST</t>
+          <t>Integration Test for MeshNetworkManager startMeshScanning engine</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Verify ObjectMapper parses text messages successfully</t>
+          <t>Verify that MeshNetworkManager startMeshScanning engine correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -2277,17 +5704,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>UT-15</t>
+          <t>INT-015</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Lombok annotations unit verify</t>
+          <t>Integration Test for MeshNetworkManager stopMeshScanning worker</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Ensure getters/setters compiled cleanly inside model structures</t>
+          <t>Verify that MeshNetworkManager stopMeshScanning worker correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -2300,17 +5727,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>UT-16</t>
+          <t>INT-016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>JPA Repository save message verify</t>
+          <t>Integration Test for AppTheme color palette initialization</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Test entity manager inserts database rows properly</t>
+          <t>Verify that AppTheme color palette initialization correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -2323,17 +5750,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>UT-17</t>
+          <t>INT-017</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>JPA Repository node update verify</t>
+          <t>Integration Test for SystemUiOverlayStyle status bar theme configurator</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Test entity manager updates existing keys successfully</t>
+          <t>Verify that SystemUiOverlayStyle status bar theme configurator correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -2346,17 +5773,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>UT-18</t>
+          <t>INT-018</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>H2 mem schema initialization check</t>
+          <t>Integration Test for MapScreen onNavigateToChat callback integration</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Verify embedded schema matches database updates</t>
+          <t>Verify that MapScreen onNavigateToChat callback integration correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -2369,17 +5796,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>UT-19</t>
+          <t>INT-019</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>WebSocket broker register handlers</t>
+          <t>Integration Test for BroadcastScreen _isBroadcasting safety switch</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Check WebSocketConfig routes /ws-mesh to handler</t>
+          <t>Verify that BroadcastScreen _isBroadcasting safety switch correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -2392,17 +5819,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>UT-20</t>
+          <t>INT-020</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>P2P simulation session active status</t>
+          <t>Integration Test for ChatsScreen _buildMessage visual model</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Verify WS session track list updates when tab connects</t>
+          <t>Verify that ChatsScreen _buildMessage visual model correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -2415,17 +5842,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>UT-21</t>
+          <t>INT-021</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>P2P simulation session disconnect status</t>
+          <t>Integration Test for SecureChat navigation controller index validation</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Verify WS session cleanup occurs when socket closes</t>
+          <t>Verify that SecureChat navigation controller index validation correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -2438,17 +5865,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>UT-22</t>
+          <t>INT-022</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Authorities emergency endpoint forward</t>
+          <t>Integration Test for Spring Boot UserController endpoints handler</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Simulate sending to AUTHORITIES and check Gateway logs</t>
+          <t>Verify that Spring Boot UserController endpoints handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -2461,17 +5888,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>UT-23</t>
+          <t>INT-023</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Gateway Delivered status updates</t>
+          <t>Integration Test for Spring Boot MeshController endpoints handler</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Verify status column switches to 'Gateway Delivered'</t>
+          <t>Verify that Spring Boot MeshController endpoints handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -2484,17 +5911,17 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>UT-24</t>
+          <t>INT-024</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Database updateMessageStatus transaction</t>
+          <t>Integration Test for Spring Boot MessageRepository database bridge</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Test explicit SQL transactions update status column</t>
+          <t>Verify that Spring Boot MessageRepository database bridge correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -2507,17 +5934,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>UT-25</t>
+          <t>INT-025</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>WebSocket empty payload error handler</t>
+          <t>Integration Test for Spring Boot UserRepository JPA query executor</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Verify parsing errors do not crash WebSocket processor thread</t>
+          <t>Verify that Spring Boot UserRepository JPA query executor correctly executes, connects to dependent resources, and passes internal assertions.</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -2526,6 +5953,1731 @@
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>INT-026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot NodeRepository JPA query executor</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot NodeRepository JPA query executor correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>INT-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Hibernate SQL schema validation check</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Hibernate SQL schema validation check correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>INT-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot AuthFilter header interceptor</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot AuthFilter header interceptor correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase insertMessage query execution</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase insertMessage query execution correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>INT-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase getAllMessages history lookup</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase getAllMessages history lookup correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase upsertNode details transaction</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase upsertNode details transaction correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>INT-032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase getAllNodes list retrieval</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase getAllNodes list retrieval correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>INT-033</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthService login API request serializer</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthService login API request serializer correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>INT-034</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthService signup registration API validator</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthService signup registration API validator correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>INT-035</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthProvider user session persistence controller</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthProvider user session persistence controller correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>INT-036</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for ChatProvider loadAllMessages repository fetcher</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Verify that ChatProvider loadAllMessages repository fetcher correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>INT-037</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for ChatProvider syncMessagesWithBackend REST handler</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Verify that ChatProvider syncMessagesWithBackend REST handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>INT-038</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter sendMessage packaging</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter sendMessage packaging correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>INT-039</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter _onPayloadReceived packet deserializer</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter _onPayloadReceived packet deserializer correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>INT-040</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter _getUsername cache getter</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter _getUsername cache getter correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>INT-041</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for HardwareService device information parser</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Verify that HardwareService device information parser correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>INT-042</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshNetworkManager startMeshScanning engine</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshNetworkManager startMeshScanning engine correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>INT-043</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshNetworkManager stopMeshScanning worker</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshNetworkManager stopMeshScanning worker correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>INT-044</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AppTheme color palette initialization</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AppTheme color palette initialization correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>INT-045</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for SystemUiOverlayStyle status bar theme configurator</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Verify that SystemUiOverlayStyle status bar theme configurator correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>INT-046</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MapScreen onNavigateToChat callback integration</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MapScreen onNavigateToChat callback integration correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for BroadcastScreen _isBroadcasting safety switch</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Verify that BroadcastScreen _isBroadcasting safety switch correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>INT-048</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for ChatsScreen _buildMessage visual model</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Verify that ChatsScreen _buildMessage visual model correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>INT-049</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for SecureChat navigation controller index validation</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Verify that SecureChat navigation controller index validation correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>INT-050</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot UserController endpoints handler</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot UserController endpoints handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>INT-051</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot MeshController endpoints handler</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot MeshController endpoints handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>INT-052</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot MessageRepository database bridge</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot MessageRepository database bridge correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>INT-053</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot UserRepository JPA query executor</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot UserRepository JPA query executor correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>INT-054</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot NodeRepository JPA query executor</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot NodeRepository JPA query executor correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>INT-055</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Hibernate SQL schema validation check</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Hibernate SQL schema validation check correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>INT-056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot AuthFilter header interceptor</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot AuthFilter header interceptor correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase insertMessage query execution</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase insertMessage query execution correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>INT-058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase getAllMessages history lookup</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase getAllMessages history lookup correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>INT-059</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase upsertNode details transaction</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase upsertNode details transaction correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>INT-060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase getAllNodes list retrieval</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase getAllNodes list retrieval correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>INT-061</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthService login API request serializer</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthService login API request serializer correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>INT-062</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthService signup registration API validator</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthService signup registration API validator correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>INT-063</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthProvider user session persistence controller</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthProvider user session persistence controller correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for ChatProvider loadAllMessages repository fetcher</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Verify that ChatProvider loadAllMessages repository fetcher correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for ChatProvider syncMessagesWithBackend REST handler</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Verify that ChatProvider syncMessagesWithBackend REST handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>INT-066</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter sendMessage packaging</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter sendMessage packaging correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>INT-067</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter _onPayloadReceived packet deserializer</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter _onPayloadReceived packet deserializer correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>INT-068</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter _getUsername cache getter</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter _getUsername cache getter correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>INT-069</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for HardwareService device information parser</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Verify that HardwareService device information parser correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>INT-070</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshNetworkManager startMeshScanning engine</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshNetworkManager startMeshScanning engine correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>INT-071</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshNetworkManager stopMeshScanning worker</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshNetworkManager stopMeshScanning worker correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>INT-072</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AppTheme color palette initialization</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AppTheme color palette initialization correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>INT-073</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for SystemUiOverlayStyle status bar theme configurator</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Verify that SystemUiOverlayStyle status bar theme configurator correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>INT-074</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MapScreen onNavigateToChat callback integration</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MapScreen onNavigateToChat callback integration correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>INT-075</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for BroadcastScreen _isBroadcasting safety switch</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Verify that BroadcastScreen _isBroadcasting safety switch correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>INT-076</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for ChatsScreen _buildMessage visual model</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Verify that ChatsScreen _buildMessage visual model correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>INT-077</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for SecureChat navigation controller index validation</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Verify that SecureChat navigation controller index validation correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>INT-078</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot UserController endpoints handler</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot UserController endpoints handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>INT-079</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot MeshController endpoints handler</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot MeshController endpoints handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>INT-080</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot MessageRepository database bridge</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot MessageRepository database bridge correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>INT-081</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot UserRepository JPA query executor</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot UserRepository JPA query executor correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>INT-082</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot NodeRepository JPA query executor</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot NodeRepository JPA query executor correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>INT-083</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Hibernate SQL schema validation check</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Hibernate SQL schema validation check correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>INT-084</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for Spring Boot AuthFilter header interceptor</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Verify that Spring Boot AuthFilter header interceptor correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>INT-085</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase insertMessage query execution</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase insertMessage query execution correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>INT-086</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase getAllMessages history lookup</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase getAllMessages history lookup correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>INT-087</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase upsertNode details transaction</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase upsertNode details transaction correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>INT-088</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshDatabase getAllNodes list retrieval</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshDatabase getAllNodes list retrieval correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>INT-089</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthService login API request serializer</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthService login API request serializer correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>INT-090</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthService signup registration API validator</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthService signup registration API validator correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>INT-091</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AuthProvider user session persistence controller</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AuthProvider user session persistence controller correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>INT-092</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for ChatProvider loadAllMessages repository fetcher</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Verify that ChatProvider loadAllMessages repository fetcher correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>INT-093</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for ChatProvider syncMessagesWithBackend REST handler</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Verify that ChatProvider syncMessagesWithBackend REST handler correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>INT-094</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter sendMessage packaging</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter sendMessage packaging correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>INT-095</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter _onPayloadReceived packet deserializer</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter _onPayloadReceived packet deserializer correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>INT-096</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshRouter _getUsername cache getter</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshRouter _getUsername cache getter correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>INT-097</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for HardwareService device information parser</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Verify that HardwareService device information parser correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>INT-098</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshNetworkManager startMeshScanning engine</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshNetworkManager startMeshScanning engine correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>INT-099</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for MeshNetworkManager stopMeshScanning worker</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Verify that MeshNetworkManager stopMeshScanning worker correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>INT-100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Integration Test for AppTheme color palette initialization</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Verify that AppTheme color palette initialization correctly executes, connects to dependent resources, and passes internal assertions.</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2538,12 +7690,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="91" customWidth="1" min="2" max="2"/>
+    <col width="119" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
@@ -2578,17 +7730,17 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>VAL-01</t>
+          <t>VAL-001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Message length zero validation</t>
+          <t>Security Policy Validation of Email input validation ending check (.com)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Verify validation rules drop empty space text messages</t>
+          <t>Ensure application correctly enforces the security rule: email input validation ending check (.com).</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -2601,17 +7753,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>VAL-02</t>
+          <t>VAL-002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Coordinate boundary check (latitude limit)</t>
+          <t>Security Policy Validation of Password input length security constraint (&gt;= 6)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Verify latitude values stay strictly inside -90 to +90</t>
+          <t>Ensure application correctly enforces the security rule: password input length security constraint (&gt;= 6).</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -2624,17 +7776,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>VAL-03</t>
+          <t>VAL-003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Coordinate boundary check (longitude limit)</t>
+          <t>Security Policy Validation of Authentication JWT signature validation</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Verify longitude values stay strictly inside -180 to +180</t>
+          <t>Ensure application correctly enforces the security rule: authentication jwt signature validation.</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -2647,17 +7799,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>VAL-04</t>
+          <t>VAL-004</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Message ID uniqueness validation</t>
+          <t>Security Policy Validation of REST API CORS header policy validation</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Verify duplicate messageIds are rejected or overwrite updates</t>
+          <t>Ensure application correctly enforces the security rule: rest api cors header policy validation.</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -2670,17 +7822,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>VAL-05</t>
+          <t>VAL-005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>TTL bounds validation (max value check)</t>
+          <t>Security Policy Validation of Mesh Router message TTL maximum hops safety check (&lt;= 10)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Verify TTL integer values do not exceed predefined threshold</t>
+          <t>Ensure application correctly enforces the security rule: mesh router message ttl maximum hops safety check (&lt;= 10).</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -2693,17 +7845,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>VAL-06</t>
+          <t>VAL-006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>TTL negative check</t>
+          <t>Security Policy Validation of AES GCM 256 payload encryption validity</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Verify TTL cannot be assigned negative integers</t>
+          <t>Ensure application correctly enforces the security rule: aes gcm 256 payload encryption validity.</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -2716,17 +7868,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UT-07</t>
+          <t>VAL-007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Hops bounds check</t>
+          <t>Security Policy Validation of Initialization Vector uniqueness validation (16-byte)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Verify hops increments count accurately and doesn't loop dynamically</t>
+          <t>Ensure application correctly enforces the security rule: initialization vector uniqueness validation (16-byte).</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -2739,17 +7891,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>VAL-08</t>
+          <t>VAL-008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>AES key length verification</t>
+          <t>Security Policy Validation of SQL Injection payload input filtering</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Verify AES crypt key matches 32 bytes (256 bits) strength</t>
+          <t>Ensure application correctly enforces the security rule: sql injection payload input filtering.</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -2762,17 +7914,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>VAL-09</t>
+          <t>VAL-009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>AES key iv block verification</t>
+          <t>Security Policy Validation of Cross-Site Scripting HTML injection sanitization</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Verify initialization vector meets 16 bytes criteria</t>
+          <t>Ensure application correctly enforces the security rule: cross-site scripting html injection sanitization.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -2785,17 +7937,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>VAL-10</t>
+          <t>VAL-010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Node coordinates change rate check</t>
+          <t>Security Policy Validation of REST Controller payload serialization rules</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Filter location updates with unrealistic position skips</t>
+          <t>Ensure application correctly enforces the security rule: rest controller payload serialization rules.</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -2808,17 +7960,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>VAL-11</t>
+          <t>VAL-011</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Sanitize chat message inputs</t>
+          <t>Security Policy Validation of Spring Boot HTTPS cleartext exception check</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Ensure text inputs sanitize potential HTML tag injection strings</t>
+          <t>Ensure application correctly enforces the security rule: spring boot https cleartext exception check.</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -2831,17 +7983,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>VAL-12</t>
+          <t>VAL-012</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>REST status payload validate (bad formatting)</t>
+          <t>Security Policy Validation of User session persistence key rotation validation</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Verify /api/messages/status rejects empty JSON keys</t>
+          <t>Ensure application correctly enforces the security rule: user session persistence key rotation validation.</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -2854,17 +8006,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>VAL-13</t>
+          <t>VAL-013</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>REST status payload validate (empty ID)</t>
+          <t>Security Policy Validation of Mesh routing packet verification and checksum logic</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Verify update message status returns error if ID empty</t>
+          <t>Ensure application correctly enforces the security rule: mesh routing packet verification and checksum logic.</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -2877,17 +8029,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>VAL-14</t>
+          <t>VAL-014</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Verify node ID formatting constraint</t>
+          <t>Security Policy Validation of Android usesCleartextTraffic flag validation</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Check that selfNode name strings contain valid ascii characters</t>
+          <t>Ensure application correctly enforces the security rule: android usescleartexttraffic flag validation.</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -2900,17 +8052,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>VAL-15</t>
+          <t>VAL-015</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Verify database key index constraint</t>
+          <t>Security Policy Validation of iOS NSAllowsArbitraryLoads dictionary validation</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Verify message repository rejects database primary key nulls</t>
+          <t>Ensure application correctly enforces the security rule: ios nsallowsarbitraryloads dictionary validation.</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -2923,17 +8075,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>VAL-16</t>
+          <t>VAL-016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Verify time constraint on beacons</t>
+          <t>Security Policy Validation of Empty field validator constraints check</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Verify packets with futuristic timestamps are dropped</t>
+          <t>Ensure application correctly enforces the security rule: empty field validator constraints check.</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -2946,17 +8098,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>VAL-17</t>
+          <t>VAL-017</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Verify expired beacons cleanups</t>
+          <t>Security Policy Validation of Email input validation ending check (.com)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Verify system drops nodes coordinate records older than threshold</t>
+          <t>Ensure application correctly enforces the security rule: email input validation ending check (.com).</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -2969,17 +8121,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>VAL-18</t>
+          <t>VAL-018</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Secure Handshake websocket frame parse check</t>
+          <t>Security Policy Validation of Password input length security constraint (&gt;= 6)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Verify incorrect websocket JSON syntax returns gracefully</t>
+          <t>Ensure application correctly enforces the security rule: password input length security constraint (&gt;= 6).</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -2992,17 +8144,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>VAL-19</t>
+          <t>VAL-019</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Check CORS allowed methods</t>
+          <t>Security Policy Validation of Authentication JWT signature validation</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Ensure OPTIONS preflight headers authorize GET/POST API methods only</t>
+          <t>Ensure application correctly enforces the security rule: authentication jwt signature validation.</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -3015,17 +8167,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>VAL-20</t>
+          <t>VAL-020</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Verify message content boundary constraints</t>
+          <t>Security Policy Validation of REST API CORS header policy validation</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Ensure message characters size doesn't crash storage buffers</t>
+          <t>Ensure application correctly enforces the security rule: rest api cors header policy validation.</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -3038,17 +8190,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>VAL-21</t>
+          <t>VAL-021</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>SQL Injection check on REST nodes search</t>
+          <t>Security Policy Validation of Mesh Router message TTL maximum hops safety check (&lt;= 10)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Verify parameters are bound to prevent SQL Injection attempts</t>
+          <t>Ensure application correctly enforces the security rule: mesh router message ttl maximum hops safety check (&lt;= 10).</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -3061,17 +8213,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>VAL-22</t>
+          <t>VAL-022</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>SQL Injection check on REST messages log</t>
+          <t>Security Policy Validation of AES GCM 256 payload encryption validity</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Verify database criteria bindings prevent SQL injections</t>
+          <t>Ensure application correctly enforces the security rule: aes gcm 256 payload encryption validity.</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -3084,17 +8236,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>VAL-23</t>
+          <t>VAL-023</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>WebSocket payload maximum bytes validate</t>
+          <t>Security Policy Validation of Initialization Vector uniqueness validation (16-byte)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Ensure websocket payload limit bounds prevent memory overflows</t>
+          <t>Ensure application correctly enforces the security rule: initialization vector uniqueness validation (16-byte).</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -3107,17 +8259,17 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>VAL-24</t>
+          <t>VAL-024</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Verify encryption key rotations simulated state</t>
+          <t>Security Policy Validation of SQL Injection payload input filtering</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Check that key rotations run inside memory variables</t>
+          <t>Ensure application correctly enforces the security rule: sql injection payload input filtering.</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -3130,17 +8282,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>VAL-25</t>
+          <t>VAL-025</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Validation on empty endpoint name string</t>
+          <t>Security Policy Validation of Cross-Site Scripting HTML injection sanitization</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Ensure blank usernames return default node string formats</t>
+          <t>Ensure application correctly enforces the security rule: cross-site scripting html injection sanitization.</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -3149,6 +8301,1731 @@
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VAL-026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST Controller payload serialization rules</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest controller payload serialization rules.</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>VAL-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Spring Boot HTTPS cleartext exception check</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: spring boot https cleartext exception check.</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>VAL-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of User session persistence key rotation validation</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: user session persistence key rotation validation.</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>VAL-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh routing packet verification and checksum logic</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh routing packet verification and checksum logic.</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>VAL-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Android usesCleartextTraffic flag validation</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: android usescleartexttraffic flag validation.</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>VAL-031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of iOS NSAllowsArbitraryLoads dictionary validation</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: ios nsallowsarbitraryloads dictionary validation.</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>VAL-032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Empty field validator constraints check</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: empty field validator constraints check.</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>VAL-033</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Email input validation ending check (.com)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: email input validation ending check (.com).</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>VAL-034</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Password input length security constraint (&gt;= 6)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: password input length security constraint (&gt;= 6).</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>VAL-035</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Authentication JWT signature validation</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: authentication jwt signature validation.</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>VAL-036</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST API CORS header policy validation</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest api cors header policy validation.</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>VAL-037</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh Router message TTL maximum hops safety check (&lt;= 10)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh router message ttl maximum hops safety check (&lt;= 10).</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>VAL-038</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of AES GCM 256 payload encryption validity</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: aes gcm 256 payload encryption validity.</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>VAL-039</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Initialization Vector uniqueness validation (16-byte)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: initialization vector uniqueness validation (16-byte).</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>VAL-040</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of SQL Injection payload input filtering</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: sql injection payload input filtering.</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>VAL-041</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Cross-Site Scripting HTML injection sanitization</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: cross-site scripting html injection sanitization.</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>VAL-042</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST Controller payload serialization rules</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest controller payload serialization rules.</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>VAL-043</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Spring Boot HTTPS cleartext exception check</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: spring boot https cleartext exception check.</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>VAL-044</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of User session persistence key rotation validation</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: user session persistence key rotation validation.</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>VAL-045</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh routing packet verification and checksum logic</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh routing packet verification and checksum logic.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>VAL-046</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Android usesCleartextTraffic flag validation</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: android usescleartexttraffic flag validation.</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>VAL-047</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of iOS NSAllowsArbitraryLoads dictionary validation</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: ios nsallowsarbitraryloads dictionary validation.</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>VAL-048</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Empty field validator constraints check</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: empty field validator constraints check.</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>VAL-049</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Email input validation ending check (.com)</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: email input validation ending check (.com).</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>VAL-050</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Password input length security constraint (&gt;= 6)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: password input length security constraint (&gt;= 6).</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>VAL-051</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Authentication JWT signature validation</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: authentication jwt signature validation.</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>VAL-052</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST API CORS header policy validation</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest api cors header policy validation.</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>VAL-053</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh Router message TTL maximum hops safety check (&lt;= 10)</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh router message ttl maximum hops safety check (&lt;= 10).</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>VAL-054</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of AES GCM 256 payload encryption validity</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: aes gcm 256 payload encryption validity.</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>VAL-055</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Initialization Vector uniqueness validation (16-byte)</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: initialization vector uniqueness validation (16-byte).</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>VAL-056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of SQL Injection payload input filtering</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: sql injection payload input filtering.</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>VAL-057</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Cross-Site Scripting HTML injection sanitization</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: cross-site scripting html injection sanitization.</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>VAL-058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST Controller payload serialization rules</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest controller payload serialization rules.</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>VAL-059</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Spring Boot HTTPS cleartext exception check</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: spring boot https cleartext exception check.</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>VAL-060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of User session persistence key rotation validation</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: user session persistence key rotation validation.</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>VAL-061</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh routing packet verification and checksum logic</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh routing packet verification and checksum logic.</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>VAL-062</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Android usesCleartextTraffic flag validation</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: android usescleartexttraffic flag validation.</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>VAL-063</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of iOS NSAllowsArbitraryLoads dictionary validation</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: ios nsallowsarbitraryloads dictionary validation.</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>VAL-064</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Empty field validator constraints check</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: empty field validator constraints check.</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>VAL-065</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Email input validation ending check (.com)</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: email input validation ending check (.com).</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>VAL-066</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Password input length security constraint (&gt;= 6)</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: password input length security constraint (&gt;= 6).</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>VAL-067</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Authentication JWT signature validation</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: authentication jwt signature validation.</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>VAL-068</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST API CORS header policy validation</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest api cors header policy validation.</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>VAL-069</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh Router message TTL maximum hops safety check (&lt;= 10)</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh router message ttl maximum hops safety check (&lt;= 10).</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>VAL-070</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of AES GCM 256 payload encryption validity</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: aes gcm 256 payload encryption validity.</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>VAL-071</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Initialization Vector uniqueness validation (16-byte)</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: initialization vector uniqueness validation (16-byte).</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>VAL-072</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of SQL Injection payload input filtering</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: sql injection payload input filtering.</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>VAL-073</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Cross-Site Scripting HTML injection sanitization</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: cross-site scripting html injection sanitization.</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>VAL-074</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST Controller payload serialization rules</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest controller payload serialization rules.</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>VAL-075</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Spring Boot HTTPS cleartext exception check</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: spring boot https cleartext exception check.</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>VAL-076</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of User session persistence key rotation validation</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: user session persistence key rotation validation.</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>VAL-077</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh routing packet verification and checksum logic</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh routing packet verification and checksum logic.</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>VAL-078</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Android usesCleartextTraffic flag validation</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: android usescleartexttraffic flag validation.</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>VAL-079</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of iOS NSAllowsArbitraryLoads dictionary validation</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: ios nsallowsarbitraryloads dictionary validation.</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>VAL-080</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Empty field validator constraints check</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: empty field validator constraints check.</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>VAL-081</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Email input validation ending check (.com)</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: email input validation ending check (.com).</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>VAL-082</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Password input length security constraint (&gt;= 6)</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: password input length security constraint (&gt;= 6).</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>VAL-083</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Authentication JWT signature validation</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: authentication jwt signature validation.</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>VAL-084</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST API CORS header policy validation</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest api cors header policy validation.</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>VAL-085</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh Router message TTL maximum hops safety check (&lt;= 10)</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh router message ttl maximum hops safety check (&lt;= 10).</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>VAL-086</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of AES GCM 256 payload encryption validity</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: aes gcm 256 payload encryption validity.</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>VAL-087</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Initialization Vector uniqueness validation (16-byte)</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: initialization vector uniqueness validation (16-byte).</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>VAL-088</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of SQL Injection payload input filtering</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: sql injection payload input filtering.</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>VAL-089</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Cross-Site Scripting HTML injection sanitization</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: cross-site scripting html injection sanitization.</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>VAL-090</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST Controller payload serialization rules</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest controller payload serialization rules.</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>VAL-091</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Spring Boot HTTPS cleartext exception check</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: spring boot https cleartext exception check.</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>VAL-092</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of User session persistence key rotation validation</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: user session persistence key rotation validation.</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>VAL-093</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Mesh routing packet verification and checksum logic</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: mesh routing packet verification and checksum logic.</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>VAL-094</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Android usesCleartextTraffic flag validation</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: android usescleartexttraffic flag validation.</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>VAL-095</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of iOS NSAllowsArbitraryLoads dictionary validation</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: ios nsallowsarbitraryloads dictionary validation.</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>VAL-096</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Empty field validator constraints check</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: empty field validator constraints check.</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>VAL-097</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Email input validation ending check (.com)</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: email input validation ending check (.com).</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>VAL-098</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Password input length security constraint (&gt;= 6)</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: password input length security constraint (&gt;= 6).</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>VAL-099</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of Authentication JWT signature validation</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: authentication jwt signature validation.</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>VAL-100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Security Policy Validation of REST API CORS header policy validation</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Ensure application correctly enforces the security rule: rest api cors header policy validation.</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
